--- a/onlinePracticeTestUploadForm.xlsx
+++ b/onlinePracticeTestUploadForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwk90\GitHub\ntest_receipt_module\NTestReceipt4\resources\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwk90\development\GitHub\sample_files_repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B9C59A-38BC-427E-979F-8444B1322B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB50370C-ABC2-4E7F-979A-EFA1BE48A48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9090" yWindow="2520" windowWidth="14760" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35265" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>test1@hotmail.com</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -133,6 +133,35 @@
         <scheme val="minor"/>
       </rPr>
       <t>에는 마지막번호가 4글자가 되도록 해주세요! ID생성규칙이 전화번호뒷4글자+학번 으로 이뤄집니다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>※ "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" 라는 예시는 제거해주세요!</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -244,7 +273,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -531,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -571,11 +600,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E3" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
     </row>

--- a/onlinePracticeTestUploadForm.xlsx
+++ b/onlinePracticeTestUploadForm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwk90\development\GitHub\sample_files_repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB50370C-ABC2-4E7F-979A-EFA1BE48A48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0BC692-DAB4-4F64-884C-5B1504ACB9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35265" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>test1@hotmail.com</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,6 +135,9 @@
       <t>에는 마지막번호가 4글자가 되도록 해주세요! ID생성규칙이 전화번호뒷4글자+학번 으로 이뤄집니다.</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">※ </t>
   </si>
   <si>
     <r>
@@ -560,16 +563,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
     <col min="4" max="4" width="22.625" customWidth="1"/>
+    <col min="5" max="5" width="41.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -586,7 +590,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>20202020</v>
       </c>
@@ -600,17 +604,22 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E4" s="4" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/onlinePracticeTestUploadForm.xlsx
+++ b/onlinePracticeTestUploadForm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwk90\development\GitHub\sample_files_repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0BC692-DAB4-4F64-884C-5B1504ACB9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BACDDF-9EC3-4A84-A029-F70AA78C51C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35265" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,7 +141,7 @@
   </si>
   <si>
     <r>
-      <t>※ "</t>
+      <t xml:space="preserve">   ("</t>
     </r>
     <r>
       <rPr>
@@ -164,7 +164,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>" 라는 예시는 제거해주세요!</t>
+      <t>" 라는 예시는 삭제하고 입력해주세요.)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -570,7 +570,7 @@
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
     <col min="4" max="4" width="22.625" customWidth="1"/>
-    <col min="5" max="5" width="41.625" customWidth="1"/>
+    <col min="5" max="5" width="46.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
